--- a/4P_Index_Loi_2020-04_Produits_Plastiques.xlsx
+++ b/4P_Index_Loi_2020-04_Produits_Plastiques.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -584,7 +584,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
+          <t>Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
+          <t>Flagship plastics law: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return and extended producer responsibility; set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclables.</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -605,7 +605,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
+          <t>Art. 4: prohibits single-use or disposable plastic products (cups, cutlery, straws, sachets); Art. 5: prohibits checkout plastic bags regardless of thickness; Art. 16: producers must integrate a share of recycled plastic in new products (targets set by decree); Art. 19: import of plastic waste into national territory is prohibited.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
+          <t>Law adopted by the National Assembly on 30 December 2019 and promulgated 8 January 2020 as Law No. 2020-04. Parliamentary legislation (≠0.75 executive regulation).</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
+          <t>production, consumption, retail, waste management, recycling, industry, packaging, environment</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -629,15 +629,15 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
+          <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
+          <t>Art. 21: floor price for recyclers buying plastic waste (set by decree); Art. 22: plastic tax on non-recyclable plastic products (rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years.</t>
         </is>
       </c>
       <c r="O2" s="3">
@@ -649,12 +649,12 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Art. 1: 'La présente loi fixe les règles relatives à la prévention et la réduction de l impact sur l environnement et la santé humaine des produits en plastique et à la gestion écologique rationnelle des déchets plastiques' / 'This law sets rules on preventing and reducing environmental and human-health impacts of plastic products and on rational ecological management of plastic waste'.</t>
+          <t>Art. 4: prohibits production, import, detention for sale, sale, supply and use of single-use or disposable plastic products, including cups/glasses/lids, cutlery/plates, straws/stirrers, and water/beverage sachets.</t>
         </is>
       </c>
       <c r="S2" s="2" t="n">
@@ -665,7 +665,7 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>Art. 2: applies to products made from plastic materials (single-use or not) and resulting waste; Art. 42: enters into force 3 months after JO publication; Art. 41: implementing decrees.</t>
+          <t>Art. 26: manufacture/import — 1–3 years imprisonment and FCFA 5–10 million fine (+0.25 enforcement); Art. 25: control agents from Environment, Health, Industry, Commerce, Finance ministries (+0.25 authority); Art. 23: seizure of prohibited products (+0.25 monitoring). Art. 4 exception for primary food packaging.</t>
         </is>
       </c>
       <c r="V2" s="3">
@@ -674,14 +674,14 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Loi-cadre phare — remplace et abroge la Loi 2015-09 (Art. 40). / Flagship framework law — replaces and repeals Law 2015-09 (Art. 40).</t>
+          <t>Central single-use plastic ban. Exception for transparent recyclable primary food packaging reduces unconditionality.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
+          <t>Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
+          <t>Flagship plastics law: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return and extended producer responsibility; set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclables.</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -702,7 +702,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
+          <t>Art. 4: prohibits single-use or disposable plastic products (cups, cutlery, straws, sachets); Art. 5: prohibits checkout plastic bags regardless of thickness; Art. 16: producers must integrate a share of recycled plastic in new products (targets set by decree); Art. 19: import of plastic waste into national territory is prohibited.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -710,7 +710,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
+          <t>Law adopted by the National Assembly on 30 December 2019 and promulgated 8 January 2020 as Law No. 2020-04. Parliamentary legislation (≠0.75 executive regulation).</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
+          <t>production, consumption, retail, waste management, recycling, industry, packaging, environment</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -726,15 +726,15 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
+          <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
+          <t>Art. 21: floor price for recyclers buying plastic waste (set by decree); Art. 22: plastic tax on non-recyclable plastic products (rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years.</t>
         </is>
       </c>
       <c r="O3" s="3">
@@ -746,12 +746,12 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Art. 4: prohibits production, import, detention for sale, sale, supply and use of 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products', including cups/glasses/lids, cutlery/plates, straws/stirrers, and sachets for water/beverages.</t>
+          <t>Art. 5: checkout plastic bags are prohibited regardless of thickness (including biodegradable/oxo-degradable bags).</t>
         </is>
       </c>
       <c r="S3" s="2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>Art. 26: manufacture/import offence — 1–3 years imprisonment and FCFA 5–10 million fine; Art. 27: sale/use offence — 1–3 months and FCFA 50,000–100,000; Art. 23: seizure of prohibited products.</t>
+          <t>Art. 27: sale/use offence — 1–3 months imprisonment and FCFA 50,000–100,000 (+0.25 enforcement); Art. 25: designated control ministries (+0.25 authority); Art. 5(2) exception for transparent recyclable bags at point of sale for food protection (+0.25 monitoring via controls).</t>
         </is>
       </c>
       <c r="V3" s="3">
@@ -771,14 +771,14 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>Interdiction centrale des plastiques à usage unique — bien au-delà des sachets fins de 2015-09. / Central single-use plastic ban — far beyond 2015-09 thin-bag scope.</t>
+          <t>Checkout bag ban with narrow food-packaging exception.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
+          <t>Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
+          <t>Flagship plastics law: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return and extended producer responsibility; set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclables.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -799,7 +799,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
+          <t>Art. 4: prohibits single-use or disposable plastic products (cups, cutlery, straws, sachets); Art. 5: prohibits checkout plastic bags regardless of thickness; Art. 16: producers must integrate a share of recycled plastic in new products (targets set by decree); Art. 19: import of plastic waste into national territory is prohibited.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
+          <t>Law adopted by the National Assembly on 30 December 2019 and promulgated 8 January 2020 as Law No. 2020-04. Parliamentary legislation (≠0.75 executive regulation).</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -815,7 +815,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
+          <t>production, consumption, retail, waste management, recycling, industry, packaging, environment</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -823,15 +823,15 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
+          <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
+          <t>Art. 21: floor price for recyclers buying plastic waste (set by decree); Art. 22: plastic tax on non-recyclable plastic products (rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years.</t>
         </is>
       </c>
       <c r="O4" s="3">
@@ -839,27 +839,27 @@
         <v/>
       </c>
       <c r="P4" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Consumption</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>Art. 5: 'Les sacs plastiques sortie de caisse... sont interdits, quelle que soit leur épaisseur' / 'Checkout plastic bags... are prohibited regardless of thickness' (with or without handles/straps; includes biodegradable/oxo-degradable bags per exposé des motifs).</t>
+          <t>Arts. 6–7: deposit required on purchase of products in plastic bottles; amount set by decree; sellers must accept returned bottles and deliver to nearest collection point.</t>
         </is>
       </c>
       <c r="S4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>Art. 5(2): exception for transparent recyclable bags used at point of sale to package food for protection/handling (producer to consumer); import subject to prior Environment Minister authorisation.</t>
+          <t>Art. 33: refusal penalty — 15 days to 1 month imprisonment and FCFA 50,000–100,000 (+0.25 enforcement); deposit amount and modalities set by subordinate decree (+0.25 authority). No monitoring mechanism in law text.</t>
         </is>
       </c>
       <c r="V4" s="3">
@@ -868,14 +868,14 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>Interdiction des sacs caisse — exception emballage alimentaire primaire transparent recyclable. / Checkout bag ban — exception for transparent recyclable primary food packaging.</t>
+          <t>Deposit-return scheme; operative but deposit amount requires implementing decree.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
+          <t>Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
+          <t>Flagship plastics law: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return and extended producer responsibility; set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclables.</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
+          <t>Art. 4: prohibits single-use or disposable plastic products (cups, cutlery, straws, sachets); Art. 5: prohibits checkout plastic bags regardless of thickness; Art. 16: producers must integrate a share of recycled plastic in new products (targets set by decree); Art. 19: import of plastic waste into national territory is prohibited.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
+          <t>Law adopted by the National Assembly on 30 December 2019 and promulgated 8 January 2020 as Law No. 2020-04. Parliamentary legislation (≠0.75 executive regulation).</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
+          <t>production, consumption, retail, waste management, recycling, industry, packaging, environment</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
@@ -920,15 +920,15 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
+          <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
+          <t>Art. 21: floor price for recyclers buying plastic waste (set by decree); Art. 22: plastic tax on non-recyclable plastic products (rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years.</t>
         </is>
       </c>
       <c r="O5" s="3">
@@ -940,23 +940,23 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Recycling</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>Art. 6: 'Une consigne est exigée à l achat de tout produit contenu dans des bouteilles en plastique' / 'A deposit is required on purchase of any product in plastic bottles'; amount set by decree, collected by seller and refunded on return of empty bottle.</t>
+          <t>Arts. 8–10: producers must establish collection points for plastic bottles and recover collected bottles prioritising reuse, recycling then other recovery; biannual sectoral report to Environment Minister.</t>
         </is>
       </c>
       <c r="S5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>Art. 7: sellers must accept returned bottles and deliver to nearest collection point; Art. 33: refusal penalty — 15 days to 1 month imprisonment and FCFA 50,000–100,000.</t>
+          <t>Art. 34: insufficient collection points — 3–6 months and FCFA 5–10 million (+0.25 enforcement); Art. 9–10: biannual reporting on market vs collected volumes (+0.25 monitoring); producer obligations mandatory (+0.25 authority, +0.25 unconditional).</t>
         </is>
       </c>
       <c r="V5" s="3">
@@ -965,14 +965,14 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>Système de consigne bouteilles PET — instrument de collecte direct. / Plastic-bottle deposit-return system — direct collection instrument.</t>
+          <t>Bottle-producer collection and recovery obligations.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
+          <t>Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
+          <t>Flagship plastics law: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return and extended producer responsibility; set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclables.</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -993,7 +993,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
+          <t>Art. 4: prohibits single-use or disposable plastic products (cups, cutlery, straws, sachets); Art. 5: prohibits checkout plastic bags regardless of thickness; Art. 16: producers must integrate a share of recycled plastic in new products (targets set by decree); Art. 19: import of plastic waste into national territory is prohibited.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
+          <t>Law adopted by the National Assembly on 30 December 2019 and promulgated 8 January 2020 as Law No. 2020-04. Parliamentary legislation (≠0.75 executive regulation).</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
+          <t>production, consumption, retail, waste management, recycling, industry, packaging, environment</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -1017,15 +1017,15 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
+          <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
+          <t>Art. 21: floor price for recyclers buying plastic waste (set by decree); Art. 22: plastic tax on non-recyclable plastic products (rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years.</t>
         </is>
       </c>
       <c r="O6" s="3">
@@ -1037,23 +1037,23 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Waste management</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Art. 8: producers must establish collection points for plastic bottles and 'valoriser ou faire valoriser' / 'recover or have recovered' collected bottles prioritising reuse, recycling then other recovery.</t>
+          <t>Art. 11: producers placing plastic products on the market are responsible for managing waste generated by these products (extended producer responsibility); compliance via individual programmes or accredited eco-organisms (Arts. 12–14).</t>
         </is>
       </c>
       <c r="S6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>Arts. 9–10: biannual sectoral report to Environment Minister (market vs collected volumes, collection points, gap measures); Art. 34: insufficient collection points — 3–6 months and FCFA 5–10 million.</t>
+          <t>Art. 35: EPR non-compliance — 1–3 years and FCFA 10–20 million (+0.25 enforcement); Arts. 12–14: ministerial approval, periodic controls, annual reporting (+0.25 monitoring, +0.25 authority).</t>
         </is>
       </c>
       <c r="V6" s="3">
@@ -1062,14 +1062,14 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>Obligations producteurs bouteilles — points de collecte et valorisation. / Bottle-producer obligations — collection points and recovery.</t>
+          <t>EPR framework including operational mechanisms in Arts. 12–14.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
+          <t>Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
+          <t>Flagship plastics law: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return and extended producer responsibility; set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclables.</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
+          <t>Art. 4: prohibits single-use or disposable plastic products (cups, cutlery, straws, sachets); Art. 5: prohibits checkout plastic bags regardless of thickness; Art. 16: producers must integrate a share of recycled plastic in new products (targets set by decree); Art. 19: import of plastic waste into national territory is prohibited.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
+          <t>Law adopted by the National Assembly on 30 December 2019 and promulgated 8 January 2020 as Law No. 2020-04. Parliamentary legislation (≠0.75 executive regulation).</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
+          <t>production, consumption, retail, waste management, recycling, industry, packaging, environment</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -1114,15 +1114,15 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
+          <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
+          <t>Art. 21: floor price for recyclers buying plastic waste (set by decree); Art. 22: plastic tax on non-recyclable plastic products (rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years.</t>
         </is>
       </c>
       <c r="O7" s="3">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Art. 11: producers placing plastic products on the market are 'responsables de la gestion des déchets générés par ces produits' / 'responsible for managing waste generated by these products' (extended producer responsibility); may comply via individual programmes or eco-organisms.</t>
+          <t>Arts. 15–16: producers must reduce waste at source and, when technically and economically viable, integrate a share of recycled plastic in new plastic products; decree sets national targets and deadlines.</t>
         </is>
       </c>
       <c r="S7" s="2" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>Art. 35: EPR non-compliance — 1–3 years imprisonment and FCFA 10–20 million; Arts. 12–14: approved individual programmes (3-year renewable) and accredited eco-organisms (max 10 years).</t>
+          <t>Art. 32: non-compliance — 1–3 months and FCFA 5–10 million when viable (+0.25 enforcement); specific targets set by subordinate decree (+0.25 authority). Viability condition reduces unconditionality.</t>
         </is>
       </c>
       <c r="V7" s="3">
@@ -1159,14 +1159,14 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>REP/EPR — pilier de la gouvernance déchets plastiques post-consommation. / EPR — pillar of post-consumer plastic-waste governance.</t>
+          <t>Recycled-content targets; operative framework but numeric targets in implementing decree.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
+          <t>Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
+          <t>Flagship plastics law: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return and extended producer responsibility; set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclables.</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
+          <t>Art. 4: prohibits single-use or disposable plastic products (cups, cutlery, straws, sachets); Art. 5: prohibits checkout plastic bags regardless of thickness; Art. 16: producers must integrate a share of recycled plastic in new products (targets set by decree); Art. 19: import of plastic waste into national territory is prohibited.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
+          <t>Law adopted by the National Assembly on 30 December 2019 and promulgated 8 January 2020 as Law No. 2020-04. Parliamentary legislation (≠0.75 executive regulation).</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
+          <t>production, consumption, retail, waste management, recycling, industry, packaging, environment</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -1211,15 +1211,15 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
+          <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
+          <t>Art. 21: floor price for recyclers buying plastic waste (set by decree); Art. 22: plastic tax on non-recyclable plastic products (rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years.</t>
         </is>
       </c>
       <c r="O8" s="3">
@@ -1227,27 +1227,27 @@
         <v/>
       </c>
       <c r="P8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Waste management</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Art. 19: import of plastic waste into national territory is prohibited; illegal imports seized and re-exported. Art. 20: exports only with Environment Minister authorisation.</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>Art. 12: individual collection/treatment programmes approved by Environment Ministerial order for 3 years (renewable); minimum requirements by order; periodic sworn-agent controls; suspension up to 3 months or permanent cessation for non-compliance.</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>0.5</v>
-      </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>Art. 13: eco-organisms improve selective collection and treatment; 10-year max accreditation; charter with assigned objectives; Art. 14: annual activity report by 30 April.</t>
+          <t>Art. 28–29: illegal import/unauthorised export — 3–5 years and FCFA 50–100 million (+0.25 enforcement); Art. 25: control agents designated (+0.25 authority); seizure mechanism (+0.25 monitoring).</t>
         </is>
       </c>
       <c r="V8" s="3">
@@ -1256,14 +1256,14 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>Mécanismes opérationnels REP — programmes individuels et éco-organismes. / Operational EPR mechanisms — individual programmes and eco-organisms.</t>
+          <t>Cross-border plastic-waste controls.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
+          <t>Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
+          <t>Flagship plastics law: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return and extended producer responsibility; set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclables.</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
+          <t>Art. 4: prohibits single-use or disposable plastic products (cups, cutlery, straws, sachets); Art. 5: prohibits checkout plastic bags regardless of thickness; Art. 16: producers must integrate a share of recycled plastic in new products (targets set by decree); Art. 19: import of plastic waste into national territory is prohibited.</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
+          <t>Law adopted by the National Assembly on 30 December 2019 and promulgated 8 January 2020 as Law No. 2020-04. Parliamentary legislation (≠0.75 executive regulation).</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
+          <t>production, consumption, retail, waste management, recycling, industry, packaging, environment</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -1308,15 +1308,15 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
+          <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
+          <t>Art. 21: floor price for recyclers buying plastic waste (set by decree); Art. 22: plastic tax on non-recyclable plastic products (rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years.</t>
         </is>
       </c>
       <c r="O9" s="3">
@@ -1324,16 +1324,16 @@
         <v/>
       </c>
       <c r="P9" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Recycling</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Art. 15: producers must reduce waste at source and market products that, once waste, can be 'recyclés ou valorisés' / 'recycled or recovered' in environmentally sound conditions.</t>
+          <t>Art. 21: floor price at which recycling enterprises must buy plastic waste per kg (set by decree). Art. 22: plastic tax on non-recyclable plastic products (product list and rates by decree).</t>
         </is>
       </c>
       <c r="S9" s="2" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>Exposé des motifs: systemic approach — production reduction, resource efficiency, circular economy transition.</t>
+          <t>Art. 31: buying below floor price — FCFA 2–5 million fine (+0.25 enforcement); rates and product lists set by decree (+0.25 authority). No monitoring mechanism in law text.</t>
         </is>
       </c>
       <c r="V9" s="3">
@@ -1353,14 +1353,14 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>Prévention à la source — réduction des déchets plastiques en amont. / Source prevention — upstream plastic-waste reduction.</t>
+          <t>Economic instruments; operative framework pending implementing decrees for rates.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
+          <t>Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
+          <t>Flagship plastics law: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return and extended producer responsibility; set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclables.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
+          <t>Art. 4: prohibits single-use or disposable plastic products (cups, cutlery, straws, sachets); Art. 5: prohibits checkout plastic bags regardless of thickness; Art. 16: producers must integrate a share of recycled plastic in new products (targets set by decree); Art. 19: import of plastic waste into national territory is prohibited.</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
+          <t>Law adopted by the National Assembly on 30 December 2019 and promulgated 8 January 2020 as Law No. 2020-04. Parliamentary legislation (≠0.75 executive regulation).</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
+          <t>production, consumption, retail, waste management, recycling, industry, packaging, environment</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -1405,15 +1405,15 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
+          <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
+          <t>Art. 21: floor price for recyclers buying plastic waste (set by decree); Art. 22: plastic tax on non-recyclable plastic products (rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years.</t>
         </is>
       </c>
       <c r="O10" s="3">
@@ -1425,23 +1425,23 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Waste management</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Art. 16: when technically feasible and economically viable, producers must integrate 'une part de plastique recyclé dans les produits plastiques neufs' / 'a share of recycled plastic in new plastic products'; decree sets national recycled-content targets and deadlines.</t>
+          <t>Arts. 23–25, 37: seizure of prohibited products; consumers must deliver plastic waste to designated collection points; abandoning waste outside collection points penalised.</t>
         </is>
       </c>
       <c r="S10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>Art. 32: non-compliance — 1–3 months imprisonment and FCFA 5–10 million fine when technically/economically viable.</t>
+          <t>Art. 37: abandoning plastic waste — 15 days to 1 month and FCFA 20,000–50,000 (+0.25 enforcement); Art. 39: corporate penalties including closure and confiscation (+0.25 authority, +0.25 monitoring).</t>
         </is>
       </c>
       <c r="V10" s="3">
@@ -1450,589 +1450,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>Objectifs de contenu recyclé — levier économie circulaire. / Recycled-content targets — circular-economy lever.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.au-senegal.com/IMG/pdf/loi-plastique-senegal-2020-04.pdf</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
-        </is>
-      </c>
-      <c r="O11" s="3">
-        <f>AVERAGE(G11,I11,K11,M11,P11)</f>
-        <v/>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Distribution</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>Art. 17: plastic products placed on the market must bear visible, legible, indelible marking on packaging or product indicating producer identity/company name and address.</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>Art. 30: marking breach — 3–6 months imprisonment and FCFA 2–5 million fine.</t>
-        </is>
-      </c>
-      <c r="V11" s="3">
-        <f>AVERAGE(P11,T11)</f>
-        <v/>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>Traçabilité producteur — soutient le contrôle et la REP. / Producer traceability — supports enforcement and EPR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.au-senegal.com/IMG/pdf/loi-plastique-senegal-2020-04.pdf</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
-        </is>
-      </c>
-      <c r="O12" s="3">
-        <f>AVERAGE(G12,I12,K12,M12,P12)</f>
-        <v/>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Disposal</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>Art. 18: consumers and end-users must, when plastic products become waste, 'les acheminer vers les points de collectes aménagés à cet effet' / 'deliver them to designated collection points'.</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>Art. 37: abandoning plastic waste outside collection points — 15 days to 1 month imprisonment and FCFA 20,000–50,000.</t>
-        </is>
-      </c>
-      <c r="V12" s="3">
-        <f>AVERAGE(P12,T12)</f>
-        <v/>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>Obligation consommateur — acheminement vers points de collecte. / Consumer obligation — deliver to collection points.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.au-senegal.com/IMG/pdf/loi-plastique-senegal-2020-04.pdf</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
-        </is>
-      </c>
-      <c r="O13" s="3">
-        <f>AVERAGE(G13,I13,K13,M13,P13)</f>
-        <v/>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>Art. 19: 'L importation de déchets plastiques sur le territoire national est interdite' / 'Import of plastic waste into national territory is prohibited'; illegal imports seized and re-exported at importer's cost. Art. 20: exports only with Environment Minister authorisation to countries with adequate treatment facilities.</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>Art. 28: illegal import — 3–5 years and FCFA 50–100 million; Art. 29: unauthorised export — same penalties.</t>
-        </is>
-      </c>
-      <c r="V13" s="3">
-        <f>AVERAGE(P13,T13)</f>
-        <v/>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>Contrôle transfrontalier des déchets plastiques — alignement Convention de Bâle. / Cross-border plastic-waste control — Basel Convention alignment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.au-senegal.com/IMG/pdf/loi-plastique-senegal-2020-04.pdf</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
-        </is>
-      </c>
-      <c r="O14" s="3">
-        <f>AVERAGE(G14,I14,K14,M14,P14)</f>
-        <v/>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Valorisation</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>Art. 21: establishes a 'prix plancher' / 'floor price' at which recycling enterprises must buy plastic waste per kg (set by decree). Art. 22: institutes 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (product list, rates and collection by decree).</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>Art. 31: buying below floor price — FCFA 2–5 million fine; tax incentivises recyclable materials.</t>
-        </is>
-      </c>
-      <c r="V14" s="3">
-        <f>AVERAGE(P14,T14)</f>
-        <v/>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>Instruments financiers/fiscaux — soutien au recyclage et pénalisation du non-recyclable. / Financial/fiscal instruments — support recycling and penalise non-recyclables.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.au-senegal.com/IMG/pdf/loi-plastique-senegal-2020-04.pdf</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
-        </is>
-      </c>
-      <c r="O15" s="3">
-        <f>AVERAGE(G15,I15,K15,M15,P15)</f>
-        <v/>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>Art. 23: prohibited products held or placed on the market are seized by control agents (Art. 25: Environment, Health, Industry, Commerce, Finance ministries). Art. 24: financial settlement for offences under Arts. 26, 27, 30, 31, 33, 37.</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>Art. 39: corporate penalties include fines up to 5× individual max, closure up to 5 years, confiscation, publication.</t>
-        </is>
-      </c>
-      <c r="V15" s="3">
-        <f>AVERAGE(P15,T15)</f>
-        <v/>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>Mécanismes d'application — saisie, transaction et sanctions personnes morales. / Enforcement mechanisms — seizure, settlement and corporate sanctions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Loi n° 2020-04 du 8 janvier 2020 relative à la prévention et à la réduction de l'incidence sur l'environnement des produits plastiques / Law No. 2020-04 of 8 January 2020 on prevention and reduction of environmental impacts of plastic products</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.au-senegal.com/IMG/pdf/loi-plastique-senegal-2020-04.pdf</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Loi phare sur les plastiques remplaçant la Loi 2015-09 : interdire les produits plastiques à usage unique/jetables et les sacs sortie de caisse ; instaurer la consigne sur les bouteilles en plastique ; mettre en place la responsabilité élargie des producteurs (REP/EPR) ; fixer des objectifs de contenu recyclé ; interdire l'importation de déchets plastiques ; instituer un prix plancher pour le recyclage et une taxe plastique sur les produits non recyclables. / Flagship plastics law replacing Law 2015-09: ban single-use/disposable plastic products and checkout bags; establish plastic-bottle deposit-return; implement extended producer responsibility (EPR); set recycled-content targets; ban plastic-waste imports; institute recycling floor price and plastic tax on non-recyclable products.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Art. 4: ban on 'produits plastiques à usage unique ou produits plastiques jetables' / 'single-use or disposable plastic products' (cups, cutlery, straws, water/beverage sachets); Art. 5: ban on 'sacs plastiques sortie de caisse' / 'checkout plastic bags' regardless of thickness; Art. 16: recycled-content targets set by decree; Art. 19: 'importation de déchets plastiques... interdite' / 'import of plastic waste... prohibited'.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Loi adoptée par l'Assemblée nationale le 30 décembre 2019 et promulguée le 8 janvier 2020 en tant que Loi n° 2020-04. Il s'agit d'une loi parlementaire (≠0.75), loi phare nationale sur les produits plastiques. / Law adopted by the National Assembly on 30 December 2019 and promulgated on 8 January 2020 as Law No. 2020-04. It is parliamentary legislation (≠0.75), the national flagship law on plastic products.</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>plasturgie, fabrication, importation, commerce de détail, distribution, consommation, gestion des déchets, recyclage, environnement, santé publique / plastics manufacturing, production, import, retail, distribution, consumption, waste management, recycling, environment, public health</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>production, distribution, utilisation, collecte, recyclage, élimination, gouvernance / production, distribution, use, collection, recycling, disposal, governance</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Art. 21: 'prix plancher' / 'floor price' for recyclers buying plastic waste (set by decree); Art. 22: 'taxe plastique' / 'plastic tax' on non-recyclable plastic products (list and rates by decree); Arts. 26–39: criminal fines up to FCFA 100,000,000 and imprisonment up to 5 years; Art. 24: financial settlement option for certain offences.</t>
-        </is>
-      </c>
-      <c r="O16" s="3">
-        <f>AVERAGE(G16,I16,K16,M16,P16)</f>
-        <v/>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>Art. 40: 'La loi n° 2015-09... est abrogée' / 'Law No. 2015-09... is repealed' (thin plastic-bag ban replaced by comprehensive plastics framework).</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>Promulgated 8 January 2020; effective 3 months after JO publication; current flagship plastics law in Senegal.</t>
-        </is>
-      </c>
-      <c r="V16" s="3">
-        <f>AVERAGE(P16,T16)</f>
-        <v/>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>Abrogation Loi 2015-09 — instrument_in_force=1 pour toutes les lignes de la Loi 2020-04. / Repeal of Law 2015-09 — instrument_in_force=1 for all Law 2020-04 rows.</t>
+          <t>Enforcement and consumer delivery obligations combined as one enforcement cluster.</t>
         </is>
       </c>
     </row>
